--- a/data/trans_orig/Q17F_D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario</t>
+          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,47</t>
+          <t>3,17; 9,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,28</t>
+          <t>2,1; 9,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 12,5</t>
+          <t>2,97; 14,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,26</t>
+          <t>0,95; 7,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,73</t>
+          <t>1,78; 8,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,95</t>
+          <t>3,8; 9,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 72,88</t>
+          <t>10,24; 70,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 34,39</t>
+          <t>8,61; 33,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,73</t>
+          <t>2,77; 7,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,16</t>
+          <t>3,65; 8,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 45,02</t>
+          <t>8,51; 44,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 23,65</t>
+          <t>5,92; 23,26</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,72</t>
+          <t>3,98; 12,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,01</t>
+          <t>3,09; 9,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 17,88</t>
+          <t>3,51; 18,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 34,02</t>
+          <t>6,38; 36,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,64</t>
+          <t>4,73; 10,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 17,57</t>
+          <t>5,71; 16,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 18,31</t>
+          <t>6,19; 18,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 14,72</t>
+          <t>4,62; 13,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,97</t>
+          <t>4,92; 9,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,39</t>
+          <t>5,32; 12,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,59</t>
+          <t>6,42; 15,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 18,07</t>
+          <t>5,89; 18,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 16,89</t>
+          <t>5,23; 17,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,71</t>
+          <t>4,39; 11,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,13</t>
+          <t>5,24; 13,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 23,56</t>
+          <t>9,02; 23,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 26,44</t>
+          <t>9,9; 25,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 18,79</t>
+          <t>6,76; 18,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 42,07</t>
+          <t>9,66; 38,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,23; 44,88</t>
+          <t>17,6; 45,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 20,95</t>
+          <t>9,61; 21,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,46</t>
+          <t>6,38; 13,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 22,43</t>
+          <t>8,41; 25,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,69; 33,23</t>
+          <t>15,6; 33,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 13,81</t>
+          <t>5,06; 13,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 22,95</t>
+          <t>7,87; 22,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,56</t>
+          <t>4,53; 15,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 69,32</t>
+          <t>22,81; 67,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 18,21</t>
+          <t>7,18; 21,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 13,11</t>
+          <t>5,79; 13,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 22,13</t>
+          <t>7,34; 21,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 35,62</t>
+          <t>19,32; 37,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 15,75</t>
+          <t>7,08; 15,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 14,37</t>
+          <t>7,46; 14,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 15,35</t>
+          <t>6,76; 14,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,42; 43,74</t>
+          <t>22,54; 43,8</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 16,16</t>
+          <t>7,55; 16,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 19,71</t>
+          <t>8,18; 20,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 22,75</t>
+          <t>8,38; 24,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 54,72</t>
+          <t>19,49; 57,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 19,26</t>
+          <t>7,35; 19,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,06</t>
+          <t>6,06; 14,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 19,1</t>
+          <t>8,0; 19,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,06; 41,58</t>
+          <t>21,9; 40,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 15,9</t>
+          <t>8,24; 16,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 14,88</t>
+          <t>8,16; 15,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,73</t>
+          <t>8,83; 17,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,21; 40,71</t>
+          <t>23,07; 43,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 35,87</t>
+          <t>10,93; 41,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 22,55</t>
+          <t>10,51; 24,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,68; 24,5</t>
+          <t>9,09; 23,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,93; 40,49</t>
+          <t>18,15; 40,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,29</t>
+          <t>4,36; 11,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 24,73</t>
+          <t>8,23; 24,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 20,78</t>
+          <t>9,08; 20,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,18; 32,68</t>
+          <t>15,6; 31,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,13; 20,0</t>
+          <t>8,24; 20,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 22,32</t>
+          <t>10,56; 21,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 18,91</t>
+          <t>10,4; 19,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,91; 30,54</t>
+          <t>17,9; 30,84</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,1</t>
+          <t>2,76; 14,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,77</t>
+          <t>3,94; 11,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 18,6</t>
+          <t>6,17; 17,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,18; 27,54</t>
+          <t>12,4; 27,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,8</t>
+          <t>3,08; 10,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 19,98</t>
+          <t>6,09; 19,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 21,04</t>
+          <t>7,39; 20,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 27,03</t>
+          <t>12,8; 26,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,28</t>
+          <t>3,59; 9,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 15,25</t>
+          <t>5,77; 14,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 18,29</t>
+          <t>8,23; 17,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,7</t>
+          <t>14,27; 25,43</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,57</t>
+          <t>8,3; 14,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,19</t>
+          <t>8,15; 12,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,81</t>
+          <t>7,95; 12,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,03; 31,65</t>
+          <t>19,08; 30,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,44</t>
+          <t>7,36; 11,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,18</t>
+          <t>8,03; 12,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 18,26</t>
+          <t>11,11; 17,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,8</t>
+          <t>16,08; 24,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,49</t>
+          <t>8,25; 11,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,82</t>
+          <t>8,55; 11,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,83</t>
+          <t>10,3; 14,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 26,01</t>
+          <t>18,85; 25,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,79</t>
+          <t>15,73</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,55</t>
+          <t>12,25</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,34</t>
+          <t>3,09; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,79</t>
+          <t>2,34; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 14,23</t>
+          <t>3,03; 13,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,85</t>
+          <t>1,38; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,12</t>
+          <t>1,72; 7,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,76</t>
+          <t>3,83; 10,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 70,9</t>
+          <t>9,6; 63,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 33,26</t>
+          <t>7,71; 31,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,21</t>
+          <t>2,66; 6,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,42</t>
+          <t>3,53; 8,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 44,13</t>
+          <t>8,26; 44,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 23,26</t>
+          <t>6,53; 23,71</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,33</t>
+          <t>15,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,19 +823,19 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>11,68</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>7,68</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6,87</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9,34</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>13,34</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 12,62</t>
+          <t>3,93; 13,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,35</t>
+          <t>3,49; 9,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 18,25</t>
+          <t>3,55; 18,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 36,27</t>
+          <t>6,66; 41,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,75</t>
+          <t>4,64; 11,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 16,76</t>
+          <t>5,57; 17,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 18,26</t>
+          <t>6,59; 19,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,9</t>
+          <t>7,86; 20,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,64</t>
+          <t>4,96; 10,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,98</t>
+          <t>5,42; 13,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 15,22</t>
+          <t>6,18; 15,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 18,94</t>
+          <t>8,43; 22,8</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,56</t>
+          <t>12,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,02</t>
+          <t>27,24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,58</t>
+          <t>21,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 17,0</t>
+          <t>5,44; 16,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,15</t>
+          <t>4,27; 11,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,14</t>
+          <t>5,25; 12,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 23,88</t>
+          <t>8,02; 22,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,79</t>
+          <t>9,94; 27,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 18,4</t>
+          <t>6,5; 19,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 38,71</t>
+          <t>9,08; 39,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 45,25</t>
+          <t>17,92; 42,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 21,06</t>
+          <t>9,23; 20,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,41</t>
+          <t>6,36; 13,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 25,68</t>
+          <t>8,79; 24,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,6; 33,63</t>
+          <t>15,46; 32,8</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,42</t>
+          <t>34,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,86</t>
+          <t>28,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,32</t>
+          <t>31,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,51</t>
+          <t>5,22; 13,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 22,37</t>
+          <t>7,86; 22,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 15,03</t>
+          <t>4,24; 14,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,81; 67,24</t>
+          <t>21,85; 62,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 21,25</t>
+          <t>6,93; 19,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 13,28</t>
+          <t>6,04; 12,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 21,86</t>
+          <t>7,26; 21,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,32; 37,43</t>
+          <t>21,04; 38,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 15,92</t>
+          <t>6,96; 15,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,18</t>
+          <t>7,59; 14,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,84</t>
+          <t>6,76; 15,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,54; 43,8</t>
+          <t>23,59; 43,84</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,94</t>
+          <t>30,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,99</t>
+          <t>28,56</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,46</t>
+          <t>29,6</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 16,62</t>
+          <t>7,41; 16,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 20,54</t>
+          <t>8,09; 20,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 24,46</t>
+          <t>8,25; 24,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,49; 57,83</t>
+          <t>20,03; 52,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 19,61</t>
+          <t>7,43; 18,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,96</t>
+          <t>6,11; 14,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 19,91</t>
+          <t>7,73; 19,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,9; 40,12</t>
+          <t>21,38; 38,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,12</t>
+          <t>8,27; 15,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,25</t>
+          <t>8,25; 15,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 17,64</t>
+          <t>8,91; 17,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,07; 43,56</t>
+          <t>22,64; 40,06</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,74</t>
+          <t>26,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,85</t>
+          <t>20,75</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>23,41</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,93; 41,99</t>
+          <t>10,82; 35,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 24,57</t>
+          <t>10,59; 24,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,09; 23,72</t>
+          <t>8,68; 23,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 40,92</t>
+          <t>17,66; 42,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,55</t>
+          <t>4,33; 11,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 24,32</t>
+          <t>8,2; 25,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 20,61</t>
+          <t>9,1; 20,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,6; 31,86</t>
+          <t>15,41; 30,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 20,1</t>
+          <t>8,05; 21,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,81</t>
+          <t>10,36; 20,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,42</t>
+          <t>10,24; 19,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,9; 30,84</t>
+          <t>18,29; 33,15</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>21,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,18</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,06</t>
+          <t>19,41</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 14,02</t>
+          <t>2,97; 15,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,05</t>
+          <t>3,9; 11,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 17,98</t>
+          <t>6,46; 18,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,4; 27,33</t>
+          <t>13,94; 35,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 10,56</t>
+          <t>3,32; 10,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 19,5</t>
+          <t>5,88; 19,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 20,81</t>
+          <t>7,5; 21,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 26,78</t>
+          <t>13,23; 27,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,57</t>
+          <t>3,62; 9,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 14,45</t>
+          <t>6,02; 14,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,03</t>
+          <t>8,15; 17,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 25,43</t>
+          <t>14,82; 26,02</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,77</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,01</t>
+          <t>23,29</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,3</t>
+          <t>8,24; 15,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,21</t>
+          <t>8,18; 12,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,46</t>
+          <t>7,91; 12,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,08; 30,77</t>
+          <t>19,91; 31,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,28</t>
+          <t>7,57; 11,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,11</t>
+          <t>8,17; 12,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,63</t>
+          <t>10,97; 17,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,08; 24,38</t>
+          <t>19,79; 26,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,52</t>
+          <t>8,13; 11,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,49</t>
+          <t>8,67; 11,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,7</t>
+          <t>10,25; 14,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,82</t>
+          <t>20,54; 26,97</t>
         </is>
       </c>
     </row>
